--- a/docs/Medição - Faturamento Direto.xlsx
+++ b/docs/Medição - Faturamento Direto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dasartltda.sharepoint.com/sites/DasartIncorporaes-WrEngenharia/Documentos Compartilhados/OBRAS WR/WAVE BEIRA MAR/04. ENGENHARIA/4.05 TERCEIROS/FIP INSTALAÇÕES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b73f7ac4adb68b79/APP-GESTAO-CONTRATO/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{354213B7-D17A-4DD8-B0ED-5D3FA9286C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00196F86-A5CE-43F2-8490-69954D658386}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{354213B7-D17A-4DD8-B0ED-5D3FA9286C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1930E21-F269-4647-9D7E-7724D0A62806}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="601" xr2:uid="{37B66749-6C7B-43A5-9069-298DC434CDF1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="601" xr2:uid="{37B66749-6C7B-43A5-9069-298DC434CDF1}"/>
   </bookViews>
   <sheets>
     <sheet name="FÍSICO FINANCEIRO" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -938,7 +949,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="878">
   <si>
     <t>DISCIPLINA</t>
   </si>
@@ -3558,6 +3569,48 @@
   </si>
   <si>
     <t>Med 01</t>
+  </si>
+  <si>
+    <t>16.3.1</t>
+  </si>
+  <si>
+    <t>16.3.2</t>
+  </si>
+  <si>
+    <t>16.3.3</t>
+  </si>
+  <si>
+    <t>16.3.4</t>
+  </si>
+  <si>
+    <t>16.3.5</t>
+  </si>
+  <si>
+    <t>16.3.6</t>
+  </si>
+  <si>
+    <t>16.3.7</t>
+  </si>
+  <si>
+    <t>16.3.8</t>
+  </si>
+  <si>
+    <t>16.3.9</t>
+  </si>
+  <si>
+    <t>16.3.10</t>
+  </si>
+  <si>
+    <t>16.3.11</t>
+  </si>
+  <si>
+    <t>16.3.12</t>
+  </si>
+  <si>
+    <t>16.3.13</t>
+  </si>
+  <si>
+    <t>16.3.14</t>
   </si>
 </sst>
 </file>
@@ -5235,19 +5288,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{258165D8-8B86-4EDA-91B6-663F5FA48D65}" name="Tabela1" displayName="Tabela1" ref="B3:AS408" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68" headerRowCellStyle="Moeda">
-  <autoFilter ref="B3:AS408" xr:uid="{258165D8-8B86-4EDA-91B6-663F5FA48D65}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B3:AS408" xr:uid="{258165D8-8B86-4EDA-91B6-663F5FA48D65}"/>
   <tableColumns count="44">
     <tableColumn id="1" xr3:uid="{1AE06EDF-C22F-465B-8CBF-189A18D3538E}" name="NÍVEL" dataDxfId="67"/>
     <tableColumn id="2" xr3:uid="{350FC5E9-72F2-48B8-BA38-2732FF09E0C0}" name="DISCIPLINA" dataDxfId="66"/>
@@ -5681,30 +5724,30 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="B1:AS418"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="2.44140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="9" customWidth="1"/>
     <col min="4" max="4" width="9" style="9" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="9" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="69.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="17.85546875" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="25" style="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="27.42578125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="2.140625" style="10" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="1.140625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="9" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="69.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="17.88671875" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="25" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="2.109375" style="10" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="1.109375" style="10" customWidth="1"/>
     <col min="13" max="13" width="23" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="22.88671875" style="10" customWidth="1"/>
     <col min="15" max="15" width="21" style="10" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="78" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" style="88" customWidth="1"/>
-    <col min="18" max="45" width="20.7109375" style="9" customWidth="1"/>
-    <col min="46" max="16384" width="8.7109375" style="9"/>
+    <col min="16" max="16" width="10.6640625" style="78" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" style="88" customWidth="1"/>
+    <col min="18" max="45" width="20.6640625" style="9" customWidth="1"/>
+    <col min="46" max="16384" width="8.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:45" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="F1" s="12"/>
       <c r="I1" s="11">
         <f>I2/K2</f>
@@ -5775,7 +5818,7 @@
       </c>
       <c r="AS1" s="91"/>
     </row>
-    <row r="2" spans="2:45" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:45" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="92" t="s">
         <v>807</v>
       </c>
@@ -5925,7 +5968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:45" s="3" customFormat="1" ht="30" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:45" s="3" customFormat="1" ht="172.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B3" s="39" t="s">
         <v>61</v>
       </c>
@@ -6059,7 +6102,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="4" spans="2:45" s="4" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:45" s="4" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
         <v>1</v>
       </c>
@@ -6221,7 +6264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B5" s="36">
         <v>2</v>
       </c>
@@ -6358,7 +6401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B6" s="37">
         <v>3</v>
       </c>
@@ -6435,7 +6478,7 @@
       <c r="AR6" s="27"/>
       <c r="AS6" s="56"/>
     </row>
-    <row r="7" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B7" s="36">
         <v>2</v>
       </c>
@@ -6595,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B8" s="25">
         <v>3</v>
       </c>
@@ -6670,7 +6713,7 @@
       <c r="AR8" s="24"/>
       <c r="AS8" s="54"/>
     </row>
-    <row r="9" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B9" s="36">
         <v>2</v>
       </c>
@@ -6832,7 +6875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B10" s="25">
         <v>3</v>
       </c>
@@ -6909,7 +6952,7 @@
       <c r="AR10" s="24"/>
       <c r="AS10" s="54"/>
     </row>
-    <row r="11" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B11" s="36">
         <v>2</v>
       </c>
@@ -7069,7 +7112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B12" s="25">
         <v>3</v>
       </c>
@@ -7144,7 +7187,7 @@
       <c r="AR12" s="24"/>
       <c r="AS12" s="54"/>
     </row>
-    <row r="13" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B13" s="36">
         <v>2</v>
       </c>
@@ -7304,7 +7347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B14" s="25">
         <v>3</v>
       </c>
@@ -7379,7 +7422,7 @@
       <c r="AR14" s="24"/>
       <c r="AS14" s="54"/>
     </row>
-    <row r="15" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B15" s="36">
         <v>2</v>
       </c>
@@ -7539,7 +7582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25">
         <v>3</v>
       </c>
@@ -7614,7 +7657,7 @@
       <c r="AR16" s="24"/>
       <c r="AS16" s="54"/>
     </row>
-    <row r="17" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B17" s="36">
         <v>2</v>
       </c>
@@ -7774,7 +7817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B18" s="25">
         <v>3</v>
       </c>
@@ -7849,7 +7892,7 @@
       <c r="AR18" s="24"/>
       <c r="AS18" s="54"/>
     </row>
-    <row r="19" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B19" s="36">
         <v>2</v>
       </c>
@@ -8009,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B20" s="25">
         <v>3</v>
       </c>
@@ -8084,7 +8127,7 @@
       <c r="AR20" s="24"/>
       <c r="AS20" s="54"/>
     </row>
-    <row r="21" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B21" s="36">
         <v>2</v>
       </c>
@@ -8244,7 +8287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B22" s="25">
         <v>3</v>
       </c>
@@ -8319,7 +8362,7 @@
       <c r="AR22" s="24"/>
       <c r="AS22" s="54"/>
     </row>
-    <row r="23" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B23" s="36">
         <v>2</v>
       </c>
@@ -8479,7 +8522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B24" s="25">
         <v>3</v>
       </c>
@@ -8554,7 +8597,7 @@
       <c r="AR24" s="24"/>
       <c r="AS24" s="54"/>
     </row>
-    <row r="25" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B25" s="36">
         <v>2</v>
       </c>
@@ -8714,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B26" s="25">
         <v>3</v>
       </c>
@@ -8789,7 +8832,7 @@
       <c r="AR26" s="24"/>
       <c r="AS26" s="54"/>
     </row>
-    <row r="27" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B27" s="36">
         <v>2</v>
       </c>
@@ -8949,7 +8992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B28" s="25">
         <v>3</v>
       </c>
@@ -9024,7 +9067,7 @@
       <c r="AR28" s="24"/>
       <c r="AS28" s="54"/>
     </row>
-    <row r="29" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B29" s="36">
         <v>2</v>
       </c>
@@ -9184,7 +9227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B30" s="25">
         <v>3</v>
       </c>
@@ -9259,7 +9302,7 @@
       <c r="AR30" s="24"/>
       <c r="AS30" s="54"/>
     </row>
-    <row r="31" spans="2:45" s="7" customFormat="1" ht="27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:45" s="7" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B31" s="36">
         <v>2</v>
       </c>
@@ -9419,7 +9462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:45" s="6" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:45" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="25">
         <v>3</v>
       </c>
@@ -9496,7 +9539,7 @@
       <c r="AR32" s="24"/>
       <c r="AS32" s="54"/>
     </row>
-    <row r="33" spans="2:45" s="4" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:45" s="4" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B33" s="35">
         <v>1</v>
       </c>
@@ -9658,7 +9701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B34" s="38">
         <v>2</v>
       </c>
@@ -9819,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B35" s="25">
         <v>3</v>
       </c>
@@ -9894,7 +9937,7 @@
       <c r="AR35" s="24"/>
       <c r="AS35" s="54"/>
     </row>
-    <row r="36" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B36" s="38">
         <v>2</v>
       </c>
@@ -10057,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B37" s="25">
         <v>3</v>
       </c>
@@ -10134,7 +10177,7 @@
       <c r="AR37" s="24"/>
       <c r="AS37" s="54"/>
     </row>
-    <row r="38" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B38" s="38">
         <v>2</v>
       </c>
@@ -10295,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B39" s="25">
         <v>3</v>
       </c>
@@ -10372,7 +10415,7 @@
       <c r="AR39" s="24"/>
       <c r="AS39" s="54"/>
     </row>
-    <row r="40" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B40" s="38">
         <v>2</v>
       </c>
@@ -10533,7 +10576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B41" s="25">
         <v>3</v>
       </c>
@@ -10608,7 +10651,7 @@
       <c r="AR41" s="24"/>
       <c r="AS41" s="54"/>
     </row>
-    <row r="42" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:45" s="7" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B42" s="38">
         <v>2</v>
       </c>
@@ -10769,7 +10812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B43" s="25">
         <v>3</v>
       </c>
@@ -10844,7 +10887,7 @@
       <c r="AR43" s="24"/>
       <c r="AS43" s="54"/>
     </row>
-    <row r="44" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:45" s="7" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B44" s="38">
         <v>2</v>
       </c>
@@ -11005,7 +11048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B45" s="25">
         <v>3</v>
       </c>
@@ -11080,7 +11123,7 @@
       <c r="AR45" s="24"/>
       <c r="AS45" s="54"/>
     </row>
-    <row r="46" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B46" s="38">
         <v>2</v>
       </c>
@@ -11241,7 +11284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B47" s="25">
         <v>3</v>
       </c>
@@ -11318,7 +11361,7 @@
       <c r="AR47" s="24"/>
       <c r="AS47" s="54"/>
     </row>
-    <row r="48" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B48" s="38">
         <v>2</v>
       </c>
@@ -11481,7 +11524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B49" s="25">
         <v>3</v>
       </c>
@@ -11558,7 +11601,7 @@
       <c r="AR49" s="24"/>
       <c r="AS49" s="54"/>
     </row>
-    <row r="50" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B50" s="38">
         <v>2</v>
       </c>
@@ -11719,7 +11762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:45" s="1" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B51" s="25">
         <v>3</v>
       </c>
@@ -11794,7 +11837,7 @@
       <c r="AR51" s="24"/>
       <c r="AS51" s="54"/>
     </row>
-    <row r="52" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B52" s="35">
         <v>1</v>
       </c>
@@ -11956,7 +11999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B53" s="38">
         <v>2</v>
       </c>
@@ -12120,7 +12163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B54" s="25">
         <v>3</v>
       </c>
@@ -12195,7 +12238,7 @@
       <c r="AR54" s="24"/>
       <c r="AS54" s="54"/>
     </row>
-    <row r="55" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B55" s="25">
         <v>3</v>
       </c>
@@ -12270,7 +12313,7 @@
       <c r="AR55" s="24"/>
       <c r="AS55" s="54"/>
     </row>
-    <row r="56" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B56" s="25">
         <v>3</v>
       </c>
@@ -12345,7 +12388,7 @@
       <c r="AR56" s="24"/>
       <c r="AS56" s="54"/>
     </row>
-    <row r="57" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B57" s="25">
         <v>3</v>
       </c>
@@ -12427,7 +12470,7 @@
       <c r="AR57" s="24"/>
       <c r="AS57" s="54"/>
     </row>
-    <row r="58" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B58" s="25">
         <v>3</v>
       </c>
@@ -12502,7 +12545,7 @@
       <c r="AR58" s="24"/>
       <c r="AS58" s="54"/>
     </row>
-    <row r="59" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B59" s="25">
         <v>3</v>
       </c>
@@ -12577,7 +12620,7 @@
       <c r="AR59" s="24"/>
       <c r="AS59" s="54"/>
     </row>
-    <row r="60" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B60" s="25">
         <v>3</v>
       </c>
@@ -12652,7 +12695,7 @@
       <c r="AR60" s="24"/>
       <c r="AS60" s="54"/>
     </row>
-    <row r="61" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B61" s="25">
         <v>3</v>
       </c>
@@ -12733,7 +12776,7 @@
       <c r="AR61" s="24"/>
       <c r="AS61" s="54"/>
     </row>
-    <row r="62" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B62" s="25">
         <v>3</v>
       </c>
@@ -12808,7 +12851,7 @@
       <c r="AR62" s="24"/>
       <c r="AS62" s="54"/>
     </row>
-    <row r="63" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B63" s="25">
         <v>3</v>
       </c>
@@ -12883,7 +12926,7 @@
       <c r="AR63" s="24"/>
       <c r="AS63" s="54"/>
     </row>
-    <row r="64" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B64" s="25">
         <v>3</v>
       </c>
@@ -12959,7 +13002,7 @@
       <c r="AR64" s="24"/>
       <c r="AS64" s="54"/>
     </row>
-    <row r="65" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B65" s="25">
         <v>3</v>
       </c>
@@ -13034,7 +13077,7 @@
       <c r="AR65" s="24"/>
       <c r="AS65" s="54"/>
     </row>
-    <row r="66" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B66" s="25">
         <v>3</v>
       </c>
@@ -13109,7 +13152,7 @@
       <c r="AR66" s="24"/>
       <c r="AS66" s="54"/>
     </row>
-    <row r="67" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B67" s="25">
         <v>3</v>
       </c>
@@ -13184,7 +13227,7 @@
       <c r="AR67" s="24"/>
       <c r="AS67" s="54"/>
     </row>
-    <row r="68" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B68" s="25">
         <v>3</v>
       </c>
@@ -13258,7 +13301,7 @@
       <c r="AR68" s="24"/>
       <c r="AS68" s="54"/>
     </row>
-    <row r="69" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B69" s="38">
         <v>2</v>
       </c>
@@ -13422,7 +13465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B70" s="25">
         <v>3</v>
       </c>
@@ -13496,7 +13539,7 @@
       <c r="AR70" s="24"/>
       <c r="AS70" s="54"/>
     </row>
-    <row r="71" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B71" s="25">
         <v>3</v>
       </c>
@@ -13570,7 +13613,7 @@
       <c r="AR71" s="24"/>
       <c r="AS71" s="54"/>
     </row>
-    <row r="72" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B72" s="25">
         <v>3</v>
       </c>
@@ -13644,7 +13687,7 @@
       <c r="AR72" s="24"/>
       <c r="AS72" s="54"/>
     </row>
-    <row r="73" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B73" s="25">
         <v>3</v>
       </c>
@@ -13718,7 +13761,7 @@
       <c r="AR73" s="24"/>
       <c r="AS73" s="54"/>
     </row>
-    <row r="74" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B74" s="25">
         <v>3</v>
       </c>
@@ -13792,7 +13835,7 @@
       <c r="AR74" s="24"/>
       <c r="AS74" s="54"/>
     </row>
-    <row r="75" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B75" s="25">
         <v>3</v>
       </c>
@@ -13866,7 +13909,7 @@
       <c r="AR75" s="24"/>
       <c r="AS75" s="54"/>
     </row>
-    <row r="76" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B76" s="25">
         <v>3</v>
       </c>
@@ -13940,7 +13983,7 @@
       <c r="AR76" s="24"/>
       <c r="AS76" s="54"/>
     </row>
-    <row r="77" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B77" s="25">
         <v>3</v>
       </c>
@@ -14014,7 +14057,7 @@
       <c r="AR77" s="24"/>
       <c r="AS77" s="54"/>
     </row>
-    <row r="78" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B78" s="25">
         <v>3</v>
       </c>
@@ -14088,7 +14131,7 @@
       <c r="AR78" s="24"/>
       <c r="AS78" s="54"/>
     </row>
-    <row r="79" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B79" s="25">
         <v>3</v>
       </c>
@@ -14162,7 +14205,7 @@
       <c r="AR79" s="24"/>
       <c r="AS79" s="54"/>
     </row>
-    <row r="80" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B80" s="25">
         <v>3</v>
       </c>
@@ -14238,7 +14281,7 @@
       <c r="AR80" s="24"/>
       <c r="AS80" s="54"/>
     </row>
-    <row r="81" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B81" s="25">
         <v>3</v>
       </c>
@@ -14312,7 +14355,7 @@
       <c r="AR81" s="24"/>
       <c r="AS81" s="54"/>
     </row>
-    <row r="82" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B82" s="25">
         <v>3</v>
       </c>
@@ -14386,7 +14429,7 @@
       <c r="AR82" s="24"/>
       <c r="AS82" s="54"/>
     </row>
-    <row r="83" spans="2:45" s="1" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B83" s="25">
         <v>3</v>
       </c>
@@ -14460,7 +14503,7 @@
       <c r="AR83" s="24"/>
       <c r="AS83" s="54"/>
     </row>
-    <row r="84" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B84" s="35">
         <v>1</v>
       </c>
@@ -14622,7 +14665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B85" s="38">
         <v>2</v>
       </c>
@@ -14784,7 +14827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B86" s="25">
         <v>3</v>
       </c>
@@ -14861,7 +14904,7 @@
       <c r="AR86" s="24"/>
       <c r="AS86" s="54"/>
     </row>
-    <row r="87" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B87" s="25">
         <v>3</v>
       </c>
@@ -14938,7 +14981,7 @@
       <c r="AR87" s="24"/>
       <c r="AS87" s="54"/>
     </row>
-    <row r="88" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B88" s="25">
         <v>3</v>
       </c>
@@ -15015,7 +15058,7 @@
       <c r="AR88" s="24"/>
       <c r="AS88" s="54"/>
     </row>
-    <row r="89" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B89" s="25">
         <v>3</v>
       </c>
@@ -15092,7 +15135,7 @@
       <c r="AR89" s="24"/>
       <c r="AS89" s="54"/>
     </row>
-    <row r="90" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B90" s="25">
         <v>3</v>
       </c>
@@ -15169,7 +15212,7 @@
       <c r="AR90" s="24"/>
       <c r="AS90" s="54"/>
     </row>
-    <row r="91" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B91" s="25">
         <v>3</v>
       </c>
@@ -15246,7 +15289,7 @@
       <c r="AR91" s="24"/>
       <c r="AS91" s="54"/>
     </row>
-    <row r="92" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B92" s="25">
         <v>3</v>
       </c>
@@ -15323,7 +15366,7 @@
       <c r="AR92" s="24"/>
       <c r="AS92" s="54"/>
     </row>
-    <row r="93" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B93" s="25">
         <v>3</v>
       </c>
@@ -15400,7 +15443,7 @@
       <c r="AR93" s="24"/>
       <c r="AS93" s="54"/>
     </row>
-    <row r="94" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B94" s="25">
         <v>3</v>
       </c>
@@ -15476,7 +15519,7 @@
       <c r="AR94" s="24"/>
       <c r="AS94" s="54"/>
     </row>
-    <row r="95" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B95" s="25">
         <v>3</v>
       </c>
@@ -15553,7 +15596,7 @@
       <c r="AR95" s="24"/>
       <c r="AS95" s="54"/>
     </row>
-    <row r="96" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B96" s="25">
         <v>3</v>
       </c>
@@ -15629,7 +15672,7 @@
       <c r="AR96" s="24"/>
       <c r="AS96" s="54"/>
     </row>
-    <row r="97" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B97" s="25">
         <v>3</v>
       </c>
@@ -15706,7 +15749,7 @@
       <c r="AR97" s="24"/>
       <c r="AS97" s="54"/>
     </row>
-    <row r="98" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B98" s="25">
         <v>3</v>
       </c>
@@ -15783,7 +15826,7 @@
       <c r="AR98" s="24"/>
       <c r="AS98" s="54"/>
     </row>
-    <row r="99" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B99" s="25">
         <v>3</v>
       </c>
@@ -15860,7 +15903,7 @@
       <c r="AR99" s="24"/>
       <c r="AS99" s="54"/>
     </row>
-    <row r="100" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B100" s="25">
         <v>3</v>
       </c>
@@ -15937,7 +15980,7 @@
       <c r="AR100" s="24"/>
       <c r="AS100" s="54"/>
     </row>
-    <row r="101" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B101" s="38">
         <v>2</v>
       </c>
@@ -16101,7 +16144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B102" s="25">
         <v>3</v>
       </c>
@@ -16176,7 +16219,7 @@
       <c r="AR102" s="24"/>
       <c r="AS102" s="54"/>
     </row>
-    <row r="103" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B103" s="25">
         <v>3</v>
       </c>
@@ -16251,7 +16294,7 @@
       <c r="AR103" s="24"/>
       <c r="AS103" s="54"/>
     </row>
-    <row r="104" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B104" s="25">
         <v>3</v>
       </c>
@@ -16326,7 +16369,7 @@
       <c r="AR104" s="24"/>
       <c r="AS104" s="54"/>
     </row>
-    <row r="105" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B105" s="25">
         <v>3</v>
       </c>
@@ -16401,7 +16444,7 @@
       <c r="AR105" s="24"/>
       <c r="AS105" s="54"/>
     </row>
-    <row r="106" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B106" s="25">
         <v>3</v>
       </c>
@@ -16476,7 +16519,7 @@
       <c r="AR106" s="24"/>
       <c r="AS106" s="54"/>
     </row>
-    <row r="107" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B107" s="25">
         <v>3</v>
       </c>
@@ -16551,7 +16594,7 @@
       <c r="AR107" s="24"/>
       <c r="AS107" s="54"/>
     </row>
-    <row r="108" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B108" s="25">
         <v>3</v>
       </c>
@@ -16626,7 +16669,7 @@
       <c r="AR108" s="24"/>
       <c r="AS108" s="54"/>
     </row>
-    <row r="109" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B109" s="25">
         <v>3</v>
       </c>
@@ -16701,7 +16744,7 @@
       <c r="AR109" s="24"/>
       <c r="AS109" s="54"/>
     </row>
-    <row r="110" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B110" s="25">
         <v>3</v>
       </c>
@@ -16776,7 +16819,7 @@
       <c r="AR110" s="24"/>
       <c r="AS110" s="54"/>
     </row>
-    <row r="111" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B111" s="25">
         <v>3</v>
       </c>
@@ -16851,7 +16894,7 @@
       <c r="AR111" s="24"/>
       <c r="AS111" s="54"/>
     </row>
-    <row r="112" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B112" s="25">
         <v>3</v>
       </c>
@@ -16927,7 +16970,7 @@
       <c r="AR112" s="24"/>
       <c r="AS112" s="54"/>
     </row>
-    <row r="113" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B113" s="25">
         <v>3</v>
       </c>
@@ -17004,7 +17047,7 @@
       <c r="AR113" s="24"/>
       <c r="AS113" s="54"/>
     </row>
-    <row r="114" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B114" s="25">
         <v>3</v>
       </c>
@@ -17079,7 +17122,7 @@
       <c r="AR114" s="24"/>
       <c r="AS114" s="54"/>
     </row>
-    <row r="115" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B115" s="25">
         <v>3</v>
       </c>
@@ -17154,7 +17197,7 @@
       <c r="AR115" s="24"/>
       <c r="AS115" s="54"/>
     </row>
-    <row r="116" spans="2:45" s="4" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:45" s="4" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B116" s="25">
         <v>3</v>
       </c>
@@ -17229,7 +17272,7 @@
       <c r="AR116" s="24"/>
       <c r="AS116" s="54"/>
     </row>
-    <row r="117" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B117" s="38">
         <v>2</v>
       </c>
@@ -17391,7 +17434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B118" s="25">
         <v>3</v>
       </c>
@@ -17471,7 +17514,7 @@
       <c r="AR118" s="24"/>
       <c r="AS118" s="54"/>
     </row>
-    <row r="119" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B119" s="25">
         <v>3</v>
       </c>
@@ -17551,7 +17594,7 @@
       <c r="AR119" s="24"/>
       <c r="AS119" s="54"/>
     </row>
-    <row r="120" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B120" s="25">
         <v>3</v>
       </c>
@@ -17631,7 +17674,7 @@
       <c r="AR120" s="24"/>
       <c r="AS120" s="54"/>
     </row>
-    <row r="121" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B121" s="25">
         <v>3</v>
       </c>
@@ -17711,7 +17754,7 @@
       <c r="AR121" s="24"/>
       <c r="AS121" s="54"/>
     </row>
-    <row r="122" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B122" s="25">
         <v>3</v>
       </c>
@@ -17791,7 +17834,7 @@
       <c r="AR122" s="24"/>
       <c r="AS122" s="54"/>
     </row>
-    <row r="123" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B123" s="25">
         <v>3</v>
       </c>
@@ -17871,7 +17914,7 @@
       <c r="AR123" s="24"/>
       <c r="AS123" s="54"/>
     </row>
-    <row r="124" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B124" s="25">
         <v>3</v>
       </c>
@@ -17951,7 +17994,7 @@
       <c r="AR124" s="24"/>
       <c r="AS124" s="54"/>
     </row>
-    <row r="125" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B125" s="25">
         <v>3</v>
       </c>
@@ -18031,7 +18074,7 @@
       <c r="AR125" s="24"/>
       <c r="AS125" s="54"/>
     </row>
-    <row r="126" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B126" s="25">
         <v>3</v>
       </c>
@@ -18110,7 +18153,7 @@
       <c r="AR126" s="24"/>
       <c r="AS126" s="54"/>
     </row>
-    <row r="127" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B127" s="25">
         <v>3</v>
       </c>
@@ -18187,7 +18230,7 @@
       <c r="AR127" s="24"/>
       <c r="AS127" s="54"/>
     </row>
-    <row r="128" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B128" s="25">
         <v>3</v>
       </c>
@@ -18263,7 +18306,7 @@
       <c r="AR128" s="24"/>
       <c r="AS128" s="54"/>
     </row>
-    <row r="129" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B129" s="25">
         <v>3</v>
       </c>
@@ -18340,7 +18383,7 @@
       <c r="AR129" s="24"/>
       <c r="AS129" s="54"/>
     </row>
-    <row r="130" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B130" s="25">
         <v>3</v>
       </c>
@@ -18417,7 +18460,7 @@
       <c r="AR130" s="24"/>
       <c r="AS130" s="54"/>
     </row>
-    <row r="131" spans="2:45" s="1" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B131" s="25">
         <v>3</v>
       </c>
@@ -18494,7 +18537,7 @@
       <c r="AR131" s="24"/>
       <c r="AS131" s="54"/>
     </row>
-    <row r="132" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B132" s="35">
         <v>1</v>
       </c>
@@ -18656,7 +18699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B133" s="38">
         <v>2</v>
       </c>
@@ -18819,7 +18862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B134" s="25">
         <v>3</v>
       </c>
@@ -18895,7 +18938,7 @@
       <c r="AR134" s="24"/>
       <c r="AS134" s="54"/>
     </row>
-    <row r="135" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B135" s="25">
         <v>3</v>
       </c>
@@ -18971,7 +19014,7 @@
       <c r="AR135" s="24"/>
       <c r="AS135" s="54"/>
     </row>
-    <row r="136" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B136" s="25">
         <v>3</v>
       </c>
@@ -19047,7 +19090,7 @@
       <c r="AR136" s="24"/>
       <c r="AS136" s="54"/>
     </row>
-    <row r="137" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B137" s="25">
         <v>3</v>
       </c>
@@ -19123,7 +19166,7 @@
       <c r="AR137" s="24"/>
       <c r="AS137" s="54"/>
     </row>
-    <row r="138" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B138" s="25">
         <v>3</v>
       </c>
@@ -19199,7 +19242,7 @@
       <c r="AR138" s="24"/>
       <c r="AS138" s="54"/>
     </row>
-    <row r="139" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B139" s="25">
         <v>3</v>
       </c>
@@ -19275,7 +19318,7 @@
       <c r="AR139" s="24"/>
       <c r="AS139" s="54"/>
     </row>
-    <row r="140" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B140" s="25">
         <v>3</v>
       </c>
@@ -19351,7 +19394,7 @@
       <c r="AR140" s="24"/>
       <c r="AS140" s="54"/>
     </row>
-    <row r="141" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B141" s="25">
         <v>3</v>
       </c>
@@ -19427,7 +19470,7 @@
       <c r="AR141" s="24"/>
       <c r="AS141" s="54"/>
     </row>
-    <row r="142" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B142" s="25">
         <v>3</v>
       </c>
@@ -19503,7 +19546,7 @@
       <c r="AR142" s="24"/>
       <c r="AS142" s="54"/>
     </row>
-    <row r="143" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B143" s="25">
         <v>3</v>
       </c>
@@ -19579,7 +19622,7 @@
       <c r="AR143" s="24"/>
       <c r="AS143" s="54"/>
     </row>
-    <row r="144" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B144" s="25">
         <v>3</v>
       </c>
@@ -19654,7 +19697,7 @@
       <c r="AR144" s="24"/>
       <c r="AS144" s="54"/>
     </row>
-    <row r="145" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B145" s="25">
         <v>3</v>
       </c>
@@ -19730,7 +19773,7 @@
       <c r="AR145" s="24"/>
       <c r="AS145" s="54"/>
     </row>
-    <row r="146" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B146" s="25">
         <v>3</v>
       </c>
@@ -19806,7 +19849,7 @@
       <c r="AR146" s="24"/>
       <c r="AS146" s="54"/>
     </row>
-    <row r="147" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B147" s="25">
         <v>3</v>
       </c>
@@ -19882,7 +19925,7 @@
       <c r="AR147" s="24"/>
       <c r="AS147" s="54"/>
     </row>
-    <row r="148" spans="2:45" s="1" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B148" s="25">
         <v>3</v>
       </c>
@@ -19958,7 +20001,7 @@
       <c r="AR148" s="24"/>
       <c r="AS148" s="54"/>
     </row>
-    <row r="149" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B149" s="35">
         <v>1</v>
       </c>
@@ -20119,7 +20162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B150" s="38">
         <v>2</v>
       </c>
@@ -20283,7 +20326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B151" s="25">
         <v>3</v>
       </c>
@@ -20358,7 +20401,7 @@
       <c r="AR151" s="24"/>
       <c r="AS151" s="54"/>
     </row>
-    <row r="152" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B152" s="25">
         <v>3</v>
       </c>
@@ -20433,7 +20476,7 @@
       <c r="AR152" s="24"/>
       <c r="AS152" s="54"/>
     </row>
-    <row r="153" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B153" s="25">
         <v>3</v>
       </c>
@@ -20508,7 +20551,7 @@
       <c r="AR153" s="24"/>
       <c r="AS153" s="54"/>
     </row>
-    <row r="154" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B154" s="25">
         <v>3</v>
       </c>
@@ -20583,7 +20626,7 @@
       <c r="AR154" s="24"/>
       <c r="AS154" s="54"/>
     </row>
-    <row r="155" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B155" s="25">
         <v>3</v>
       </c>
@@ -20658,7 +20701,7 @@
       <c r="AR155" s="24"/>
       <c r="AS155" s="54"/>
     </row>
-    <row r="156" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B156" s="25">
         <v>3</v>
       </c>
@@ -20733,7 +20776,7 @@
       <c r="AR156" s="24"/>
       <c r="AS156" s="54"/>
     </row>
-    <row r="157" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B157" s="25">
         <v>3</v>
       </c>
@@ -20808,7 +20851,7 @@
       <c r="AR157" s="24"/>
       <c r="AS157" s="54"/>
     </row>
-    <row r="158" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B158" s="25">
         <v>3</v>
       </c>
@@ -20883,7 +20926,7 @@
       <c r="AR158" s="24"/>
       <c r="AS158" s="54"/>
     </row>
-    <row r="159" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B159" s="25">
         <v>3</v>
       </c>
@@ -20958,7 +21001,7 @@
       <c r="AR159" s="24"/>
       <c r="AS159" s="54"/>
     </row>
-    <row r="160" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B160" s="25">
         <v>3</v>
       </c>
@@ -21033,7 +21076,7 @@
       <c r="AR160" s="24"/>
       <c r="AS160" s="54"/>
     </row>
-    <row r="161" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B161" s="25">
         <v>3</v>
       </c>
@@ -21109,7 +21152,7 @@
       <c r="AR161" s="24"/>
       <c r="AS161" s="54"/>
     </row>
-    <row r="162" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B162" s="25">
         <v>3</v>
       </c>
@@ -21184,7 +21227,7 @@
       <c r="AR162" s="24"/>
       <c r="AS162" s="54"/>
     </row>
-    <row r="163" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B163" s="25">
         <v>3</v>
       </c>
@@ -21259,7 +21302,7 @@
       <c r="AR163" s="24"/>
       <c r="AS163" s="54"/>
     </row>
-    <row r="164" spans="2:45" s="1" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B164" s="25">
         <v>3</v>
       </c>
@@ -21334,7 +21377,7 @@
       <c r="AR164" s="24"/>
       <c r="AS164" s="54"/>
     </row>
-    <row r="165" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B165" s="35">
         <v>1</v>
       </c>
@@ -21495,7 +21538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B166" s="38">
         <v>2</v>
       </c>
@@ -21659,7 +21702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B167" s="25">
         <v>3</v>
       </c>
@@ -21734,7 +21777,7 @@
       <c r="AR167" s="24"/>
       <c r="AS167" s="54"/>
     </row>
-    <row r="168" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B168" s="25">
         <v>3</v>
       </c>
@@ -21809,7 +21852,7 @@
       <c r="AR168" s="24"/>
       <c r="AS168" s="54"/>
     </row>
-    <row r="169" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B169" s="25">
         <v>3</v>
       </c>
@@ -21884,7 +21927,7 @@
       <c r="AR169" s="24"/>
       <c r="AS169" s="54"/>
     </row>
-    <row r="170" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B170" s="25">
         <v>3</v>
       </c>
@@ -21966,7 +22009,7 @@
       <c r="AR170" s="24"/>
       <c r="AS170" s="54"/>
     </row>
-    <row r="171" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B171" s="25">
         <v>3</v>
       </c>
@@ -22041,7 +22084,7 @@
       <c r="AR171" s="24"/>
       <c r="AS171" s="54"/>
     </row>
-    <row r="172" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B172" s="25">
         <v>3</v>
       </c>
@@ -22116,7 +22159,7 @@
       <c r="AR172" s="24"/>
       <c r="AS172" s="54"/>
     </row>
-    <row r="173" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B173" s="25">
         <v>3</v>
       </c>
@@ -22191,7 +22234,7 @@
       <c r="AR173" s="24"/>
       <c r="AS173" s="54"/>
     </row>
-    <row r="174" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B174" s="25">
         <v>3</v>
       </c>
@@ -22266,7 +22309,7 @@
       <c r="AR174" s="24"/>
       <c r="AS174" s="54"/>
     </row>
-    <row r="175" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B175" s="25">
         <v>3</v>
       </c>
@@ -22341,7 +22384,7 @@
       <c r="AR175" s="24"/>
       <c r="AS175" s="54"/>
     </row>
-    <row r="176" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B176" s="25">
         <v>3</v>
       </c>
@@ -22417,7 +22460,7 @@
       <c r="AR176" s="24"/>
       <c r="AS176" s="54"/>
     </row>
-    <row r="177" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B177" s="25">
         <v>3</v>
       </c>
@@ -22492,7 +22535,7 @@
       <c r="AR177" s="24"/>
       <c r="AS177" s="54"/>
     </row>
-    <row r="178" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B178" s="25">
         <v>3</v>
       </c>
@@ -22567,7 +22610,7 @@
       <c r="AR178" s="24"/>
       <c r="AS178" s="54"/>
     </row>
-    <row r="179" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B179" s="35">
         <v>1</v>
       </c>
@@ -22728,7 +22771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B180" s="38">
         <v>2</v>
       </c>
@@ -22892,7 +22935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="2:45" s="7" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:45" s="7" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B181" s="25">
         <v>3</v>
       </c>
@@ -22970,7 +23013,7 @@
       <c r="AR181" s="24"/>
       <c r="AS181" s="54"/>
     </row>
-    <row r="182" spans="2:45" s="7" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:45" s="7" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B182" s="25">
         <v>3</v>
       </c>
@@ -23047,7 +23090,7 @@
       <c r="AR182" s="24"/>
       <c r="AS182" s="54"/>
     </row>
-    <row r="183" spans="2:45" s="7" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:45" s="7" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B183" s="25">
         <v>3</v>
       </c>
@@ -23124,7 +23167,7 @@
       <c r="AR183" s="24"/>
       <c r="AS183" s="54"/>
     </row>
-    <row r="184" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B184" s="25">
         <v>3</v>
       </c>
@@ -23201,7 +23244,7 @@
       <c r="AR184" s="24"/>
       <c r="AS184" s="54"/>
     </row>
-    <row r="185" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B185" s="25">
         <v>3</v>
       </c>
@@ -23278,7 +23321,7 @@
       <c r="AR185" s="24"/>
       <c r="AS185" s="54"/>
     </row>
-    <row r="186" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B186" s="25">
         <v>3</v>
       </c>
@@ -23355,7 +23398,7 @@
       <c r="AR186" s="24"/>
       <c r="AS186" s="54"/>
     </row>
-    <row r="187" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B187" s="25">
         <v>3</v>
       </c>
@@ -23432,7 +23475,7 @@
       <c r="AR187" s="24"/>
       <c r="AS187" s="54"/>
     </row>
-    <row r="188" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B188" s="25">
         <v>3</v>
       </c>
@@ -23509,7 +23552,7 @@
       <c r="AR188" s="24"/>
       <c r="AS188" s="54"/>
     </row>
-    <row r="189" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B189" s="25">
         <v>3</v>
       </c>
@@ -23586,7 +23629,7 @@
       <c r="AR189" s="24"/>
       <c r="AS189" s="54"/>
     </row>
-    <row r="190" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B190" s="25">
         <v>3</v>
       </c>
@@ -23663,7 +23706,7 @@
       <c r="AR190" s="24"/>
       <c r="AS190" s="54"/>
     </row>
-    <row r="191" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B191" s="25">
         <v>3</v>
       </c>
@@ -23740,7 +23783,7 @@
       <c r="AR191" s="24"/>
       <c r="AS191" s="54"/>
     </row>
-    <row r="192" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B192" s="25">
         <v>3</v>
       </c>
@@ -23815,7 +23858,7 @@
       <c r="AR192" s="24"/>
       <c r="AS192" s="54"/>
     </row>
-    <row r="193" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B193" s="25">
         <v>3</v>
       </c>
@@ -23889,7 +23932,7 @@
       <c r="AR193" s="24"/>
       <c r="AS193" s="54"/>
     </row>
-    <row r="194" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B194" s="25">
         <v>3</v>
       </c>
@@ -23964,7 +24007,7 @@
       <c r="AR194" s="24"/>
       <c r="AS194" s="54"/>
     </row>
-    <row r="195" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B195" s="25">
         <v>3</v>
       </c>
@@ -24039,7 +24082,7 @@
       <c r="AR195" s="24"/>
       <c r="AS195" s="54"/>
     </row>
-    <row r="196" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B196" s="25">
         <v>3</v>
       </c>
@@ -24114,7 +24157,7 @@
       <c r="AR196" s="24"/>
       <c r="AS196" s="54"/>
     </row>
-    <row r="197" spans="2:45" s="5" customFormat="1" ht="13.5" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:45" s="5" customFormat="1" ht="13.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B197" s="25">
         <v>3</v>
       </c>
@@ -24189,7 +24232,7 @@
       <c r="AR197" s="24"/>
       <c r="AS197" s="54"/>
     </row>
-    <row r="198" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B198" s="38">
         <v>2</v>
       </c>
@@ -24353,7 +24396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="2:45" s="1" customFormat="1" ht="24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:45" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B199" s="25">
         <v>3</v>
       </c>
@@ -24430,7 +24473,7 @@
       <c r="AR199" s="24"/>
       <c r="AS199" s="54"/>
     </row>
-    <row r="200" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B200" s="35">
         <v>1</v>
       </c>
@@ -24591,7 +24634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B201" s="38">
         <v>2</v>
       </c>
@@ -24755,7 +24798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B202" s="25">
         <v>3</v>
       </c>
@@ -24833,7 +24876,7 @@
       <c r="AR202" s="24"/>
       <c r="AS202" s="54"/>
     </row>
-    <row r="203" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B203" s="25">
         <v>3</v>
       </c>
@@ -24910,7 +24953,7 @@
       <c r="AR203" s="24"/>
       <c r="AS203" s="54"/>
     </row>
-    <row r="204" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B204" s="25">
         <v>3</v>
       </c>
@@ -24987,7 +25030,7 @@
       <c r="AR204" s="24"/>
       <c r="AS204" s="54"/>
     </row>
-    <row r="205" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B205" s="25">
         <v>3</v>
       </c>
@@ -25064,7 +25107,7 @@
       <c r="AR205" s="24"/>
       <c r="AS205" s="54"/>
     </row>
-    <row r="206" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B206" s="25">
         <v>3</v>
       </c>
@@ -25142,7 +25185,7 @@
       <c r="AR206" s="24"/>
       <c r="AS206" s="54"/>
     </row>
-    <row r="207" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B207" s="25">
         <v>3</v>
       </c>
@@ -25221,7 +25264,7 @@
       <c r="AR207" s="24"/>
       <c r="AS207" s="54"/>
     </row>
-    <row r="208" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B208" s="25">
         <v>3</v>
       </c>
@@ -25298,7 +25341,7 @@
       <c r="AR208" s="24"/>
       <c r="AS208" s="54"/>
     </row>
-    <row r="209" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B209" s="25">
         <v>3</v>
       </c>
@@ -25375,7 +25418,7 @@
       <c r="AR209" s="24"/>
       <c r="AS209" s="54"/>
     </row>
-    <row r="210" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B210" s="25">
         <v>3</v>
       </c>
@@ -25452,7 +25495,7 @@
       <c r="AR210" s="24"/>
       <c r="AS210" s="54"/>
     </row>
-    <row r="211" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B211" s="25">
         <v>3</v>
       </c>
@@ -25529,7 +25572,7 @@
       <c r="AR211" s="24"/>
       <c r="AS211" s="54"/>
     </row>
-    <row r="212" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B212" s="25">
         <v>3</v>
       </c>
@@ -25606,7 +25649,7 @@
       <c r="AR212" s="24"/>
       <c r="AS212" s="54"/>
     </row>
-    <row r="213" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B213" s="25">
         <v>3</v>
       </c>
@@ -25681,7 +25724,7 @@
       <c r="AR213" s="24"/>
       <c r="AS213" s="54"/>
     </row>
-    <row r="214" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B214" s="25">
         <v>3</v>
       </c>
@@ -25755,7 +25798,7 @@
       <c r="AR214" s="24"/>
       <c r="AS214" s="54"/>
     </row>
-    <row r="215" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B215" s="25">
         <v>3</v>
       </c>
@@ -25830,7 +25873,7 @@
       <c r="AR215" s="24"/>
       <c r="AS215" s="54"/>
     </row>
-    <row r="216" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B216" s="25">
         <v>3</v>
       </c>
@@ -25905,7 +25948,7 @@
       <c r="AR216" s="24"/>
       <c r="AS216" s="54"/>
     </row>
-    <row r="217" spans="2:45" s="1" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:45" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B217" s="25">
         <v>3</v>
       </c>
@@ -25980,7 +26023,7 @@
       <c r="AR217" s="24"/>
       <c r="AS217" s="54"/>
     </row>
-    <row r="218" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B218" s="35">
         <v>1</v>
       </c>
@@ -26141,7 +26184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B219" s="38">
         <v>2</v>
       </c>
@@ -26305,7 +26348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B220" s="25">
         <v>3</v>
       </c>
@@ -26379,7 +26422,7 @@
       <c r="AR220" s="24"/>
       <c r="AS220" s="54"/>
     </row>
-    <row r="221" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B221" s="25">
         <v>3</v>
       </c>
@@ -26454,7 +26497,7 @@
       <c r="AR221" s="24"/>
       <c r="AS221" s="54"/>
     </row>
-    <row r="222" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B222" s="25">
         <v>3</v>
       </c>
@@ -26529,7 +26572,7 @@
       <c r="AR222" s="24"/>
       <c r="AS222" s="54"/>
     </row>
-    <row r="223" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B223" s="25">
         <v>3</v>
       </c>
@@ -26604,7 +26647,7 @@
       <c r="AR223" s="24"/>
       <c r="AS223" s="54"/>
     </row>
-    <row r="224" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B224" s="25">
         <v>3</v>
       </c>
@@ -26679,7 +26722,7 @@
       <c r="AR224" s="24"/>
       <c r="AS224" s="54"/>
     </row>
-    <row r="225" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B225" s="25">
         <v>3</v>
       </c>
@@ -26754,7 +26797,7 @@
       <c r="AR225" s="24"/>
       <c r="AS225" s="54"/>
     </row>
-    <row r="226" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B226" s="19">
         <v>3</v>
       </c>
@@ -26819,7 +26862,7 @@
       <c r="AR226" s="24"/>
       <c r="AS226" s="54"/>
     </row>
-    <row r="227" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B227" s="22">
         <v>3</v>
       </c>
@@ -26894,7 +26937,7 @@
       <c r="AR227" s="24"/>
       <c r="AS227" s="54"/>
     </row>
-    <row r="228" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B228" s="25">
         <v>3</v>
       </c>
@@ -26969,7 +27012,7 @@
       <c r="AR228" s="24"/>
       <c r="AS228" s="54"/>
     </row>
-    <row r="229" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B229" s="25">
         <v>3</v>
       </c>
@@ -27044,7 +27087,7 @@
       <c r="AR229" s="24"/>
       <c r="AS229" s="54"/>
     </row>
-    <row r="230" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B230" s="25">
         <v>3</v>
       </c>
@@ -27119,7 +27162,7 @@
       <c r="AR230" s="24"/>
       <c r="AS230" s="54"/>
     </row>
-    <row r="231" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B231" s="25">
         <v>3</v>
       </c>
@@ -27193,7 +27236,7 @@
       <c r="AR231" s="24"/>
       <c r="AS231" s="54"/>
     </row>
-    <row r="232" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B232" s="25">
         <v>3</v>
       </c>
@@ -27268,7 +27311,7 @@
       <c r="AR232" s="24"/>
       <c r="AS232" s="54"/>
     </row>
-    <row r="233" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B233" s="25">
         <v>3</v>
       </c>
@@ -27343,7 +27386,7 @@
       <c r="AR233" s="24"/>
       <c r="AS233" s="54"/>
     </row>
-    <row r="234" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B234" s="19">
         <v>3</v>
       </c>
@@ -27418,7 +27461,7 @@
       <c r="AR234" s="24"/>
       <c r="AS234" s="54"/>
     </row>
-    <row r="235" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B235" s="38">
         <v>2</v>
       </c>
@@ -27582,7 +27625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B236" s="25">
         <v>3</v>
       </c>
@@ -27656,7 +27699,7 @@
       <c r="AR236" s="24"/>
       <c r="AS236" s="54"/>
     </row>
-    <row r="237" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B237" s="25">
         <v>3</v>
       </c>
@@ -27732,7 +27775,7 @@
       <c r="AR237" s="24"/>
       <c r="AS237" s="54"/>
     </row>
-    <row r="238" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B238" s="25">
         <v>3</v>
       </c>
@@ -27807,7 +27850,7 @@
       <c r="AR238" s="24"/>
       <c r="AS238" s="54"/>
     </row>
-    <row r="239" spans="2:45" s="7" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:45" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B239" s="37">
         <v>2</v>
       </c>
@@ -27971,7 +28014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B240" s="25">
         <v>3</v>
       </c>
@@ -28045,7 +28088,7 @@
       <c r="AR240" s="24"/>
       <c r="AS240" s="54"/>
     </row>
-    <row r="241" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B241" s="25">
         <v>3</v>
       </c>
@@ -28120,7 +28163,7 @@
       <c r="AR241" s="24"/>
       <c r="AS241" s="54"/>
     </row>
-    <row r="242" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B242" s="19">
         <v>3</v>
       </c>
@@ -28195,7 +28238,7 @@
       <c r="AR242" s="24"/>
       <c r="AS242" s="54"/>
     </row>
-    <row r="243" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B243" s="22">
         <v>3</v>
       </c>
@@ -28271,7 +28314,7 @@
       <c r="AR243" s="24"/>
       <c r="AS243" s="54"/>
     </row>
-    <row r="244" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B244" s="25">
         <v>3</v>
       </c>
@@ -28347,7 +28390,7 @@
       <c r="AR244" s="24"/>
       <c r="AS244" s="54"/>
     </row>
-    <row r="245" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B245" s="25">
         <v>3</v>
       </c>
@@ -28422,7 +28465,7 @@
       <c r="AR245" s="24"/>
       <c r="AS245" s="54"/>
     </row>
-    <row r="246" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B246" s="25">
         <v>3</v>
       </c>
@@ -28498,7 +28541,7 @@
       <c r="AR246" s="24"/>
       <c r="AS246" s="54"/>
     </row>
-    <row r="247" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B247" s="25">
         <v>3</v>
       </c>
@@ -28574,7 +28617,7 @@
       <c r="AR247" s="24"/>
       <c r="AS247" s="54"/>
     </row>
-    <row r="248" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B248" s="25">
         <v>3</v>
       </c>
@@ -28650,7 +28693,7 @@
       <c r="AR248" s="24"/>
       <c r="AS248" s="54"/>
     </row>
-    <row r="249" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B249" s="25">
         <v>3</v>
       </c>
@@ -28726,7 +28769,7 @@
       <c r="AR249" s="24"/>
       <c r="AS249" s="54"/>
     </row>
-    <row r="250" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B250" s="35">
         <v>1</v>
       </c>
@@ -28887,7 +28930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="2:45" s="8" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:45" s="8" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B251" s="38">
         <v>2</v>
       </c>
@@ -29049,7 +29092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B252" s="25">
         <v>3</v>
       </c>
@@ -29124,7 +29167,7 @@
       <c r="AR252" s="24"/>
       <c r="AS252" s="54"/>
     </row>
-    <row r="253" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B253" s="25">
         <v>3</v>
       </c>
@@ -29199,7 +29242,7 @@
       <c r="AR253" s="24"/>
       <c r="AS253" s="54"/>
     </row>
-    <row r="254" spans="2:45" s="7" customFormat="1" ht="13.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:45" s="7" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B254" s="25">
         <v>3</v>
       </c>
@@ -29275,7 +29318,7 @@
       <c r="AR254" s="24"/>
       <c r="AS254" s="54"/>
     </row>
-    <row r="255" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B255" s="35">
         <v>1</v>
       </c>
@@ -29436,7 +29479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B256" s="35">
         <v>2</v>
       </c>
@@ -29599,7 +29642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B257" s="35">
         <v>3</v>
       </c>
@@ -29675,7 +29718,7 @@
       <c r="AR257" s="24"/>
       <c r="AS257" s="54"/>
     </row>
-    <row r="258" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B258" s="35">
         <v>3</v>
       </c>
@@ -29751,7 +29794,7 @@
       <c r="AR258" s="24"/>
       <c r="AS258" s="54"/>
     </row>
-    <row r="259" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B259" s="35">
         <v>3</v>
       </c>
@@ -29827,7 +29870,7 @@
       <c r="AR259" s="24"/>
       <c r="AS259" s="54"/>
     </row>
-    <row r="260" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B260" s="35">
         <v>3</v>
       </c>
@@ -29903,7 +29946,7 @@
       <c r="AR260" s="24"/>
       <c r="AS260" s="54"/>
     </row>
-    <row r="261" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B261" s="35">
         <v>3</v>
       </c>
@@ -29979,7 +30022,7 @@
       <c r="AR261" s="24"/>
       <c r="AS261" s="54"/>
     </row>
-    <row r="262" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B262" s="35">
         <v>2</v>
       </c>
@@ -30141,7 +30184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B263" s="35">
         <v>3</v>
       </c>
@@ -30217,7 +30260,7 @@
       <c r="AR263" s="24"/>
       <c r="AS263" s="54"/>
     </row>
-    <row r="264" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B264" s="35">
         <v>3</v>
       </c>
@@ -30294,7 +30337,7 @@
       <c r="AR264" s="24"/>
       <c r="AS264" s="54"/>
     </row>
-    <row r="265" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B265" s="35">
         <v>1</v>
       </c>
@@ -30455,7 +30498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B266" s="35">
         <v>2</v>
       </c>
@@ -30619,7 +30662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B267" s="35">
         <v>3</v>
       </c>
@@ -30694,7 +30737,7 @@
       <c r="AR267" s="24"/>
       <c r="AS267" s="54"/>
     </row>
-    <row r="268" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B268" s="35">
         <v>3</v>
       </c>
@@ -30769,7 +30812,7 @@
       <c r="AR268" s="24"/>
       <c r="AS268" s="54"/>
     </row>
-    <row r="269" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B269" s="35">
         <v>3</v>
       </c>
@@ -30845,7 +30888,7 @@
       <c r="AR269" s="24"/>
       <c r="AS269" s="54"/>
     </row>
-    <row r="270" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B270" s="35">
         <v>3</v>
       </c>
@@ -30921,7 +30964,7 @@
       <c r="AR270" s="24"/>
       <c r="AS270" s="54"/>
     </row>
-    <row r="271" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B271" s="35">
         <v>3</v>
       </c>
@@ -30997,7 +31040,7 @@
       <c r="AR271" s="24"/>
       <c r="AS271" s="54"/>
     </row>
-    <row r="272" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B272" s="35">
         <v>3</v>
       </c>
@@ -31071,7 +31114,7 @@
       <c r="AR272" s="24"/>
       <c r="AS272" s="54"/>
     </row>
-    <row r="273" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B273" s="35">
         <v>3</v>
       </c>
@@ -31148,7 +31191,7 @@
       <c r="AR273" s="24"/>
       <c r="AS273" s="54"/>
     </row>
-    <row r="274" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B274" s="35">
         <v>3</v>
       </c>
@@ -31224,7 +31267,7 @@
       <c r="AR274" s="24"/>
       <c r="AS274" s="54"/>
     </row>
-    <row r="275" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B275" s="35">
         <v>2</v>
       </c>
@@ -31388,7 +31431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:45" s="5" customFormat="1" ht="28.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B276" s="35">
         <v>3</v>
       </c>
@@ -31462,7 +31505,7 @@
       <c r="AR276" s="24"/>
       <c r="AS276" s="54"/>
     </row>
-    <row r="277" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B277" s="35">
         <v>3</v>
       </c>
@@ -31536,7 +31579,7 @@
       <c r="AR277" s="24"/>
       <c r="AS277" s="54"/>
     </row>
-    <row r="278" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B278" s="35">
         <v>3</v>
       </c>
@@ -31612,7 +31655,7 @@
       <c r="AR278" s="24"/>
       <c r="AS278" s="54"/>
     </row>
-    <row r="279" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B279" s="35">
         <v>3</v>
       </c>
@@ -31688,7 +31731,7 @@
       <c r="AR279" s="24"/>
       <c r="AS279" s="54"/>
     </row>
-    <row r="280" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B280" s="35">
         <v>3</v>
       </c>
@@ -31764,7 +31807,7 @@
       <c r="AR280" s="24"/>
       <c r="AS280" s="54"/>
     </row>
-    <row r="281" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B281" s="35">
         <v>3</v>
       </c>
@@ -31840,7 +31883,7 @@
       <c r="AR281" s="24"/>
       <c r="AS281" s="54"/>
     </row>
-    <row r="282" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B282" s="35">
         <v>3</v>
       </c>
@@ -31915,7 +31958,7 @@
       <c r="AR282" s="24"/>
       <c r="AS282" s="54"/>
     </row>
-    <row r="283" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B283" s="35">
         <v>3</v>
       </c>
@@ -31991,7 +32034,7 @@
       <c r="AR283" s="24"/>
       <c r="AS283" s="54"/>
     </row>
-    <row r="284" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B284" s="35">
         <v>3</v>
       </c>
@@ -32067,7 +32110,7 @@
       <c r="AR284" s="24"/>
       <c r="AS284" s="54"/>
     </row>
-    <row r="285" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B285" s="35">
         <v>3</v>
       </c>
@@ -32143,7 +32186,7 @@
       <c r="AR285" s="24"/>
       <c r="AS285" s="54"/>
     </row>
-    <row r="286" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B286" s="35">
         <v>3</v>
       </c>
@@ -32219,7 +32262,7 @@
       <c r="AR286" s="24"/>
       <c r="AS286" s="54"/>
     </row>
-    <row r="287" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B287" s="35">
         <v>3</v>
       </c>
@@ -32295,7 +32338,7 @@
       <c r="AR287" s="24"/>
       <c r="AS287" s="54"/>
     </row>
-    <row r="288" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B288" s="35">
         <v>3</v>
       </c>
@@ -32370,7 +32413,7 @@
       <c r="AR288" s="24"/>
       <c r="AS288" s="54"/>
     </row>
-    <row r="289" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B289" s="35">
         <v>3</v>
       </c>
@@ -32447,7 +32490,7 @@
       <c r="AR289" s="24"/>
       <c r="AS289" s="54"/>
     </row>
-    <row r="290" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B290" s="35">
         <v>3</v>
       </c>
@@ -32524,7 +32567,7 @@
       <c r="AR290" s="24"/>
       <c r="AS290" s="54"/>
     </row>
-    <row r="291" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B291" s="35">
         <v>3</v>
       </c>
@@ -32601,7 +32644,7 @@
       <c r="AR291" s="24"/>
       <c r="AS291" s="54"/>
     </row>
-    <row r="292" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B292" s="35">
         <v>2</v>
       </c>
@@ -32765,7 +32808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B293" s="35">
         <v>3</v>
       </c>
@@ -32840,7 +32883,7 @@
       <c r="AR293" s="24"/>
       <c r="AS293" s="54"/>
     </row>
-    <row r="294" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B294" s="35">
         <v>1</v>
       </c>
@@ -33001,7 +33044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B295" s="35">
         <v>2</v>
       </c>
@@ -33163,7 +33206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B296" s="35">
         <v>3</v>
       </c>
@@ -33240,7 +33283,7 @@
       <c r="AR296" s="24"/>
       <c r="AS296" s="54"/>
     </row>
-    <row r="297" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B297" s="35">
         <v>3</v>
       </c>
@@ -33317,7 +33360,7 @@
       <c r="AR297" s="24"/>
       <c r="AS297" s="54"/>
     </row>
-    <row r="298" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B298" s="35">
         <v>3</v>
       </c>
@@ -33394,7 +33437,7 @@
       <c r="AR298" s="24"/>
       <c r="AS298" s="54"/>
     </row>
-    <row r="299" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B299" s="35">
         <v>3</v>
       </c>
@@ -33471,7 +33514,7 @@
       <c r="AR299" s="24"/>
       <c r="AS299" s="54"/>
     </row>
-    <row r="300" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B300" s="35">
         <v>3</v>
       </c>
@@ -33548,7 +33591,7 @@
       <c r="AR300" s="24"/>
       <c r="AS300" s="54"/>
     </row>
-    <row r="301" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B301" s="35">
         <v>3</v>
       </c>
@@ -33625,7 +33668,7 @@
       <c r="AR301" s="24"/>
       <c r="AS301" s="54"/>
     </row>
-    <row r="302" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B302" s="35">
         <v>3</v>
       </c>
@@ -33702,7 +33745,7 @@
       <c r="AR302" s="24"/>
       <c r="AS302" s="54"/>
     </row>
-    <row r="303" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B303" s="35">
         <v>3</v>
       </c>
@@ -33779,7 +33822,7 @@
       <c r="AR303" s="24"/>
       <c r="AS303" s="54"/>
     </row>
-    <row r="304" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B304" s="35">
         <v>3</v>
       </c>
@@ -33856,7 +33899,7 @@
       <c r="AR304" s="24"/>
       <c r="AS304" s="54"/>
     </row>
-    <row r="305" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B305" s="35">
         <v>3</v>
       </c>
@@ -33933,7 +33976,7 @@
       <c r="AR305" s="24"/>
       <c r="AS305" s="54"/>
     </row>
-    <row r="306" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B306" s="35">
         <v>3</v>
       </c>
@@ -34009,7 +34052,7 @@
       <c r="AR306" s="24"/>
       <c r="AS306" s="54"/>
     </row>
-    <row r="307" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B307" s="35">
         <v>3</v>
       </c>
@@ -34086,7 +34129,7 @@
       <c r="AR307" s="24"/>
       <c r="AS307" s="54"/>
     </row>
-    <row r="308" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B308" s="35">
         <v>3</v>
       </c>
@@ -34163,7 +34206,7 @@
       <c r="AR308" s="24"/>
       <c r="AS308" s="54"/>
     </row>
-    <row r="309" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B309" s="35">
         <v>3</v>
       </c>
@@ -34240,7 +34283,7 @@
       <c r="AR309" s="24"/>
       <c r="AS309" s="54"/>
     </row>
-    <row r="310" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B310" s="35">
         <v>2</v>
       </c>
@@ -34404,7 +34447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B311" s="35">
         <v>3</v>
       </c>
@@ -34479,7 +34522,7 @@
       <c r="AR311" s="24"/>
       <c r="AS311" s="54"/>
     </row>
-    <row r="312" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B312" s="35">
         <v>3</v>
       </c>
@@ -34554,7 +34597,7 @@
       <c r="AR312" s="24"/>
       <c r="AS312" s="54"/>
     </row>
-    <row r="313" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B313" s="35">
         <v>3</v>
       </c>
@@ -34629,7 +34672,7 @@
       <c r="AR313" s="24"/>
       <c r="AS313" s="54"/>
     </row>
-    <row r="314" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B314" s="35">
         <v>3</v>
       </c>
@@ -34704,7 +34747,7 @@
       <c r="AR314" s="24"/>
       <c r="AS314" s="54"/>
     </row>
-    <row r="315" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B315" s="35">
         <v>3</v>
       </c>
@@ -34779,7 +34822,7 @@
       <c r="AR315" s="24"/>
       <c r="AS315" s="54"/>
     </row>
-    <row r="316" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B316" s="35">
         <v>3</v>
       </c>
@@ -34854,7 +34897,7 @@
       <c r="AR316" s="24"/>
       <c r="AS316" s="54"/>
     </row>
-    <row r="317" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B317" s="35">
         <v>3</v>
       </c>
@@ -34929,7 +34972,7 @@
       <c r="AR317" s="24"/>
       <c r="AS317" s="54"/>
     </row>
-    <row r="318" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B318" s="35">
         <v>3</v>
       </c>
@@ -35004,7 +35047,7 @@
       <c r="AR318" s="24"/>
       <c r="AS318" s="54"/>
     </row>
-    <row r="319" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B319" s="35">
         <v>3</v>
       </c>
@@ -35079,7 +35122,7 @@
       <c r="AR319" s="24"/>
       <c r="AS319" s="54"/>
     </row>
-    <row r="320" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B320" s="35">
         <v>3</v>
       </c>
@@ -35154,7 +35197,7 @@
       <c r="AR320" s="24"/>
       <c r="AS320" s="54"/>
     </row>
-    <row r="321" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B321" s="35">
         <v>3</v>
       </c>
@@ -35230,7 +35273,7 @@
       <c r="AR321" s="24"/>
       <c r="AS321" s="54"/>
     </row>
-    <row r="322" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B322" s="35">
         <v>3</v>
       </c>
@@ -35305,7 +35348,7 @@
       <c r="AR322" s="24"/>
       <c r="AS322" s="54"/>
     </row>
-    <row r="323" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B323" s="35">
         <v>3</v>
       </c>
@@ -35380,7 +35423,7 @@
       <c r="AR323" s="24"/>
       <c r="AS323" s="54"/>
     </row>
-    <row r="324" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B324" s="35">
         <v>3</v>
       </c>
@@ -35455,7 +35498,7 @@
       <c r="AR324" s="24"/>
       <c r="AS324" s="54"/>
     </row>
-    <row r="325" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B325" s="35">
         <v>3</v>
       </c>
@@ -35530,7 +35573,7 @@
       <c r="AR325" s="24"/>
       <c r="AS325" s="54"/>
     </row>
-    <row r="326" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B326" s="35">
         <v>1</v>
       </c>
@@ -35691,7 +35734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B327" s="35">
         <v>2</v>
       </c>
@@ -35854,7 +35897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B328" s="35">
         <v>3</v>
       </c>
@@ -35930,7 +35973,7 @@
       <c r="AR328" s="24"/>
       <c r="AS328" s="54"/>
     </row>
-    <row r="329" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B329" s="35">
         <v>3</v>
       </c>
@@ -36006,7 +36049,7 @@
       <c r="AR329" s="24"/>
       <c r="AS329" s="54"/>
     </row>
-    <row r="330" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B330" s="35">
         <v>3</v>
       </c>
@@ -36082,7 +36125,7 @@
       <c r="AR330" s="24"/>
       <c r="AS330" s="54"/>
     </row>
-    <row r="331" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B331" s="35">
         <v>3</v>
       </c>
@@ -36158,7 +36201,7 @@
       <c r="AR331" s="24"/>
       <c r="AS331" s="54"/>
     </row>
-    <row r="332" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B332" s="35">
         <v>3</v>
       </c>
@@ -36234,7 +36277,7 @@
       <c r="AR332" s="24"/>
       <c r="AS332" s="54"/>
     </row>
-    <row r="333" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B333" s="35">
         <v>3</v>
       </c>
@@ -36310,7 +36353,7 @@
       <c r="AR333" s="24"/>
       <c r="AS333" s="54"/>
     </row>
-    <row r="334" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B334" s="35">
         <v>3</v>
       </c>
@@ -36386,7 +36429,7 @@
       <c r="AR334" s="24"/>
       <c r="AS334" s="54"/>
     </row>
-    <row r="335" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B335" s="35">
         <v>3</v>
       </c>
@@ -36462,7 +36505,7 @@
       <c r="AR335" s="24"/>
       <c r="AS335" s="54"/>
     </row>
-    <row r="336" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B336" s="35">
         <v>3</v>
       </c>
@@ -36538,7 +36581,7 @@
       <c r="AR336" s="24"/>
       <c r="AS336" s="54"/>
     </row>
-    <row r="337" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B337" s="35">
         <v>3</v>
       </c>
@@ -36614,7 +36657,7 @@
       <c r="AR337" s="24"/>
       <c r="AS337" s="54"/>
     </row>
-    <row r="338" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B338" s="35">
         <v>3</v>
       </c>
@@ -36689,7 +36732,7 @@
       <c r="AR338" s="24"/>
       <c r="AS338" s="54"/>
     </row>
-    <row r="339" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B339" s="35">
         <v>3</v>
       </c>
@@ -36765,7 +36808,7 @@
       <c r="AR339" s="24"/>
       <c r="AS339" s="54"/>
     </row>
-    <row r="340" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B340" s="35">
         <v>3</v>
       </c>
@@ -36841,7 +36884,7 @@
       <c r="AR340" s="24"/>
       <c r="AS340" s="54"/>
     </row>
-    <row r="341" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B341" s="35">
         <v>3</v>
       </c>
@@ -36917,7 +36960,7 @@
       <c r="AR341" s="24"/>
       <c r="AS341" s="54"/>
     </row>
-    <row r="342" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B342" s="35">
         <v>3</v>
       </c>
@@ -36992,7 +37035,7 @@
       <c r="AR342" s="24"/>
       <c r="AS342" s="54"/>
     </row>
-    <row r="343" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B343" s="35">
         <v>2</v>
       </c>
@@ -37155,7 +37198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B344" s="35">
         <v>3</v>
       </c>
@@ -37230,7 +37273,7 @@
       <c r="AR344" s="24"/>
       <c r="AS344" s="54"/>
     </row>
-    <row r="345" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B345" s="35">
         <v>3</v>
       </c>
@@ -37305,7 +37348,7 @@
       <c r="AR345" s="24"/>
       <c r="AS345" s="54"/>
     </row>
-    <row r="346" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B346" s="35">
         <v>3</v>
       </c>
@@ -37380,7 +37423,7 @@
       <c r="AR346" s="24"/>
       <c r="AS346" s="54"/>
     </row>
-    <row r="347" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B347" s="35">
         <v>3</v>
       </c>
@@ -37455,7 +37498,7 @@
       <c r="AR347" s="24"/>
       <c r="AS347" s="54"/>
     </row>
-    <row r="348" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B348" s="35">
         <v>3</v>
       </c>
@@ -37530,7 +37573,7 @@
       <c r="AR348" s="24"/>
       <c r="AS348" s="54"/>
     </row>
-    <row r="349" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B349" s="35">
         <v>3</v>
       </c>
@@ -37605,7 +37648,7 @@
       <c r="AR349" s="24"/>
       <c r="AS349" s="54"/>
     </row>
-    <row r="350" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B350" s="35">
         <v>3</v>
       </c>
@@ -37680,7 +37723,7 @@
       <c r="AR350" s="24"/>
       <c r="AS350" s="54"/>
     </row>
-    <row r="351" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B351" s="35">
         <v>3</v>
       </c>
@@ -37755,7 +37798,7 @@
       <c r="AR351" s="24"/>
       <c r="AS351" s="54"/>
     </row>
-    <row r="352" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B352" s="35">
         <v>3</v>
       </c>
@@ -37830,7 +37873,7 @@
       <c r="AR352" s="24"/>
       <c r="AS352" s="54"/>
     </row>
-    <row r="353" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B353" s="35">
         <v>3</v>
       </c>
@@ -37905,7 +37948,7 @@
       <c r="AR353" s="24"/>
       <c r="AS353" s="54"/>
     </row>
-    <row r="354" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B354" s="35">
         <v>3</v>
       </c>
@@ -37979,7 +38022,7 @@
       <c r="AR354" s="24"/>
       <c r="AS354" s="54"/>
     </row>
-    <row r="355" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B355" s="35">
         <v>3</v>
       </c>
@@ -38054,7 +38097,7 @@
       <c r="AR355" s="24"/>
       <c r="AS355" s="54"/>
     </row>
-    <row r="356" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B356" s="35">
         <v>3</v>
       </c>
@@ -38129,7 +38172,7 @@
       <c r="AR356" s="24"/>
       <c r="AS356" s="54"/>
     </row>
-    <row r="357" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B357" s="35">
         <v>3</v>
       </c>
@@ -38204,7 +38247,7 @@
       <c r="AR357" s="24"/>
       <c r="AS357" s="54"/>
     </row>
-    <row r="358" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B358" s="35">
         <v>3</v>
       </c>
@@ -38278,7 +38321,7 @@
       <c r="AR358" s="24"/>
       <c r="AS358" s="54"/>
     </row>
-    <row r="359" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B359" s="35">
         <v>2</v>
       </c>
@@ -38440,7 +38483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B360" s="35">
         <v>3</v>
       </c>
@@ -38448,11 +38491,11 @@
         <v>598</v>
       </c>
       <c r="D360" s="35" t="s">
-        <v>234</v>
+        <v>864</v>
       </c>
       <c r="E360" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.1</v>
+        <v>16.3.1</v>
       </c>
       <c r="F360" s="20" t="s">
         <v>638</v>
@@ -38517,7 +38560,7 @@
       <c r="AR360" s="24"/>
       <c r="AS360" s="54"/>
     </row>
-    <row r="361" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B361" s="35">
         <v>3</v>
       </c>
@@ -38525,11 +38568,11 @@
         <v>598</v>
       </c>
       <c r="D361" s="35" t="s">
-        <v>235</v>
+        <v>865</v>
       </c>
       <c r="E361" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.2</v>
+        <v>16.3.2</v>
       </c>
       <c r="F361" s="20" t="s">
         <v>639</v>
@@ -38594,7 +38637,7 @@
       <c r="AR361" s="24"/>
       <c r="AS361" s="54"/>
     </row>
-    <row r="362" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B362" s="35">
         <v>3</v>
       </c>
@@ -38602,11 +38645,11 @@
         <v>598</v>
       </c>
       <c r="D362" s="35" t="s">
-        <v>236</v>
+        <v>866</v>
       </c>
       <c r="E362" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.3</v>
+        <v>16.3.3</v>
       </c>
       <c r="F362" s="20" t="s">
         <v>640</v>
@@ -38671,7 +38714,7 @@
       <c r="AR362" s="24"/>
       <c r="AS362" s="54"/>
     </row>
-    <row r="363" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B363" s="35">
         <v>3</v>
       </c>
@@ -38679,11 +38722,11 @@
         <v>598</v>
       </c>
       <c r="D363" s="35" t="s">
-        <v>237</v>
+        <v>867</v>
       </c>
       <c r="E363" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.4</v>
+        <v>16.3.4</v>
       </c>
       <c r="F363" s="20" t="s">
         <v>641</v>
@@ -38748,7 +38791,7 @@
       <c r="AR363" s="24"/>
       <c r="AS363" s="54"/>
     </row>
-    <row r="364" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B364" s="35">
         <v>3</v>
       </c>
@@ -38756,11 +38799,11 @@
         <v>598</v>
       </c>
       <c r="D364" s="35" t="s">
-        <v>238</v>
+        <v>868</v>
       </c>
       <c r="E364" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.5</v>
+        <v>16.3.5</v>
       </c>
       <c r="F364" s="20" t="s">
         <v>642</v>
@@ -38825,7 +38868,7 @@
       <c r="AR364" s="24"/>
       <c r="AS364" s="54"/>
     </row>
-    <row r="365" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B365" s="35">
         <v>3</v>
       </c>
@@ -38833,11 +38876,11 @@
         <v>598</v>
       </c>
       <c r="D365" s="35" t="s">
-        <v>239</v>
+        <v>869</v>
       </c>
       <c r="E365" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.6</v>
+        <v>16.3.6</v>
       </c>
       <c r="F365" s="20" t="s">
         <v>643</v>
@@ -38902,7 +38945,7 @@
       <c r="AR365" s="24"/>
       <c r="AS365" s="54"/>
     </row>
-    <row r="366" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B366" s="35">
         <v>3</v>
       </c>
@@ -38910,11 +38953,11 @@
         <v>598</v>
       </c>
       <c r="D366" s="35" t="s">
-        <v>240</v>
+        <v>870</v>
       </c>
       <c r="E366" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.7</v>
+        <v>16.3.7</v>
       </c>
       <c r="F366" s="20" t="s">
         <v>644</v>
@@ -38979,7 +39022,7 @@
       <c r="AR366" s="24"/>
       <c r="AS366" s="54"/>
     </row>
-    <row r="367" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B367" s="35">
         <v>3</v>
       </c>
@@ -38987,11 +39030,11 @@
         <v>598</v>
       </c>
       <c r="D367" s="35" t="s">
-        <v>241</v>
+        <v>871</v>
       </c>
       <c r="E367" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.8</v>
+        <v>16.3.8</v>
       </c>
       <c r="F367" s="20" t="s">
         <v>645</v>
@@ -39056,7 +39099,7 @@
       <c r="AR367" s="24"/>
       <c r="AS367" s="54"/>
     </row>
-    <row r="368" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B368" s="35">
         <v>3</v>
       </c>
@@ -39064,11 +39107,11 @@
         <v>598</v>
       </c>
       <c r="D368" s="35" t="s">
-        <v>599</v>
+        <v>872</v>
       </c>
       <c r="E368" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.9</v>
+        <v>16.3.9</v>
       </c>
       <c r="F368" s="20" t="s">
         <v>646</v>
@@ -39133,7 +39176,7 @@
       <c r="AR368" s="24"/>
       <c r="AS368" s="54"/>
     </row>
-    <row r="369" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B369" s="35">
         <v>3</v>
       </c>
@@ -39141,11 +39184,11 @@
         <v>598</v>
       </c>
       <c r="D369" s="35" t="s">
-        <v>600</v>
+        <v>873</v>
       </c>
       <c r="E369" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.10</v>
+        <v>16.3.10</v>
       </c>
       <c r="F369" s="20" t="s">
         <v>647</v>
@@ -39210,7 +39253,7 @@
       <c r="AR369" s="24"/>
       <c r="AS369" s="54"/>
     </row>
-    <row r="370" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B370" s="35">
         <v>3</v>
       </c>
@@ -39218,11 +39261,11 @@
         <v>598</v>
       </c>
       <c r="D370" s="35" t="s">
-        <v>601</v>
+        <v>874</v>
       </c>
       <c r="E370" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.11</v>
+        <v>16.3.11</v>
       </c>
       <c r="F370" s="20" t="s">
         <v>648</v>
@@ -39286,7 +39329,7 @@
       <c r="AR370" s="24"/>
       <c r="AS370" s="54"/>
     </row>
-    <row r="371" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B371" s="35">
         <v>3</v>
       </c>
@@ -39294,11 +39337,11 @@
         <v>598</v>
       </c>
       <c r="D371" s="35" t="s">
-        <v>602</v>
+        <v>875</v>
       </c>
       <c r="E371" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.12</v>
+        <v>16.3.12</v>
       </c>
       <c r="F371" s="20" t="s">
         <v>649</v>
@@ -39363,7 +39406,7 @@
       <c r="AR371" s="24"/>
       <c r="AS371" s="54"/>
     </row>
-    <row r="372" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B372" s="35">
         <v>3</v>
       </c>
@@ -39371,11 +39414,11 @@
         <v>598</v>
       </c>
       <c r="D372" s="35" t="s">
-        <v>603</v>
+        <v>876</v>
       </c>
       <c r="E372" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.13</v>
+        <v>16.3.13</v>
       </c>
       <c r="F372" s="20" t="s">
         <v>650</v>
@@ -39440,7 +39483,7 @@
       <c r="AR372" s="24"/>
       <c r="AS372" s="54"/>
     </row>
-    <row r="373" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B373" s="35">
         <v>3</v>
       </c>
@@ -39448,11 +39491,11 @@
         <v>598</v>
       </c>
       <c r="D373" s="35" t="s">
-        <v>604</v>
+        <v>877</v>
       </c>
       <c r="E373" s="19" t="str">
         <f>TEXT(Tabela1[[#This Row],[ITEM]],"@")</f>
-        <v>16.2.14</v>
+        <v>16.3.14</v>
       </c>
       <c r="F373" s="20" t="s">
         <v>651</v>
@@ -39517,7 +39560,7 @@
       <c r="AR373" s="24"/>
       <c r="AS373" s="54"/>
     </row>
-    <row r="374" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B374" s="35">
         <v>1</v>
       </c>
@@ -39678,7 +39721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B375" s="35">
         <v>2</v>
       </c>
@@ -39841,7 +39884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="2:45" s="5" customFormat="1" ht="30" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:45" s="5" customFormat="1" ht="28.8" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B376" s="35">
         <v>3</v>
       </c>
@@ -39917,7 +39960,7 @@
       <c r="AR376" s="24"/>
       <c r="AS376" s="54"/>
     </row>
-    <row r="377" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B377" s="35">
         <v>3</v>
       </c>
@@ -39993,7 +40036,7 @@
       <c r="AR377" s="24"/>
       <c r="AS377" s="54"/>
     </row>
-    <row r="378" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B378" s="35">
         <v>3</v>
       </c>
@@ -40069,7 +40112,7 @@
       <c r="AR378" s="24"/>
       <c r="AS378" s="54"/>
     </row>
-    <row r="379" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B379" s="35">
         <v>3</v>
       </c>
@@ -40145,7 +40188,7 @@
       <c r="AR379" s="24"/>
       <c r="AS379" s="54"/>
     </row>
-    <row r="380" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B380" s="35">
         <v>3</v>
       </c>
@@ -40221,7 +40264,7 @@
       <c r="AR380" s="24"/>
       <c r="AS380" s="54"/>
     </row>
-    <row r="381" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B381" s="35">
         <v>3</v>
       </c>
@@ -40298,7 +40341,7 @@
       <c r="AR381" s="24"/>
       <c r="AS381" s="54"/>
     </row>
-    <row r="382" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B382" s="35">
         <v>3</v>
       </c>
@@ -40374,7 +40417,7 @@
       <c r="AR382" s="24"/>
       <c r="AS382" s="54"/>
     </row>
-    <row r="383" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B383" s="35">
         <v>2</v>
       </c>
@@ -40538,7 +40581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B384" s="35">
         <v>3</v>
       </c>
@@ -40613,7 +40656,7 @@
       <c r="AR384" s="24"/>
       <c r="AS384" s="54"/>
     </row>
-    <row r="385" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B385" s="35">
         <v>3</v>
       </c>
@@ -40688,7 +40731,7 @@
       <c r="AR385" s="24"/>
       <c r="AS385" s="54"/>
     </row>
-    <row r="386" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B386" s="35">
         <v>3</v>
       </c>
@@ -40764,7 +40807,7 @@
       <c r="AR386" s="24"/>
       <c r="AS386" s="54"/>
     </row>
-    <row r="387" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B387" s="35">
         <v>3</v>
       </c>
@@ -40841,7 +40884,7 @@
       <c r="AR387" s="24"/>
       <c r="AS387" s="54"/>
     </row>
-    <row r="388" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B388" s="35">
         <v>3</v>
       </c>
@@ -40916,7 +40959,7 @@
       <c r="AR388" s="24"/>
       <c r="AS388" s="54"/>
     </row>
-    <row r="389" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B389" s="35">
         <v>1</v>
       </c>
@@ -41077,7 +41120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B390" s="35">
         <v>2</v>
       </c>
@@ -41241,7 +41284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B391" s="35">
         <v>3</v>
       </c>
@@ -41320,7 +41363,7 @@
       <c r="AR391" s="24"/>
       <c r="AS391" s="54"/>
     </row>
-    <row r="392" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B392" s="35">
         <v>3</v>
       </c>
@@ -41400,7 +41443,7 @@
       <c r="AR392" s="24"/>
       <c r="AS392" s="54"/>
     </row>
-    <row r="393" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B393" s="35">
         <v>3</v>
       </c>
@@ -41477,7 +41520,7 @@
       <c r="AR393" s="24"/>
       <c r="AS393" s="54"/>
     </row>
-    <row r="394" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B394" s="35">
         <v>3</v>
       </c>
@@ -41552,7 +41595,7 @@
       <c r="AR394" s="24"/>
       <c r="AS394" s="54"/>
     </row>
-    <row r="395" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B395" s="35">
         <v>3</v>
       </c>
@@ -41627,7 +41670,7 @@
       <c r="AR395" s="24"/>
       <c r="AS395" s="54"/>
     </row>
-    <row r="396" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B396" s="35">
         <v>3</v>
       </c>
@@ -41702,7 +41745,7 @@
       <c r="AR396" s="24"/>
       <c r="AS396" s="54"/>
     </row>
-    <row r="397" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B397" s="35">
         <v>3</v>
       </c>
@@ -41777,7 +41820,7 @@
       <c r="AR397" s="24"/>
       <c r="AS397" s="54"/>
     </row>
-    <row r="398" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B398" s="35">
         <v>3</v>
       </c>
@@ -41852,7 +41895,7 @@
       <c r="AR398" s="24"/>
       <c r="AS398" s="54"/>
     </row>
-    <row r="399" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B399" s="35">
         <v>3</v>
       </c>
@@ -41927,7 +41970,7 @@
       <c r="AR399" s="24"/>
       <c r="AS399" s="54"/>
     </row>
-    <row r="400" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B400" s="35">
         <v>3</v>
       </c>
@@ -42002,7 +42045,7 @@
       <c r="AR400" s="24"/>
       <c r="AS400" s="54"/>
     </row>
-    <row r="401" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B401" s="35">
         <v>3</v>
       </c>
@@ -42077,7 +42120,7 @@
       <c r="AR401" s="24"/>
       <c r="AS401" s="54"/>
     </row>
-    <row r="402" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B402" s="35">
         <v>3</v>
       </c>
@@ -42152,7 +42195,7 @@
       <c r="AR402" s="24"/>
       <c r="AS402" s="54"/>
     </row>
-    <row r="403" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B403" s="35">
         <v>3</v>
       </c>
@@ -42227,7 +42270,7 @@
       <c r="AR403" s="24"/>
       <c r="AS403" s="54"/>
     </row>
-    <row r="404" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B404" s="35">
         <v>3</v>
       </c>
@@ -42302,7 +42345,7 @@
       <c r="AR404" s="24"/>
       <c r="AS404" s="54"/>
     </row>
-    <row r="405" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B405" s="35">
         <v>1</v>
       </c>
@@ -42463,7 +42506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="2:45" s="7" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:45" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B406" s="37">
         <v>2</v>
       </c>
@@ -42627,7 +42670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="2:45" s="5" customFormat="1" ht="15" hidden="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:45" s="5" customFormat="1" ht="14.4" collapsed="1" x14ac:dyDescent="0.3">
       <c r="B407" s="35">
         <v>3</v>
       </c>
@@ -42705,7 +42748,7 @@
       <c r="AR407" s="24"/>
       <c r="AS407" s="54"/>
     </row>
-    <row r="408" spans="2:45" s="5" customFormat="1" ht="15.75" hidden="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:45" s="5" customFormat="1" ht="15" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B408" s="35">
         <v>3</v>
       </c>
@@ -42784,7 +42827,7 @@
       <c r="AR408" s="60"/>
       <c r="AS408" s="61"/>
     </row>
-    <row r="416" spans="2:45" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:45" x14ac:dyDescent="0.3">
       <c r="O416" s="33"/>
       <c r="P416" s="77"/>
       <c r="Q416" s="79"/>
@@ -42805,7 +42848,7 @@
       <c r="AF416" s="32"/>
       <c r="AG416" s="32"/>
     </row>
-    <row r="418" spans="18:33" x14ac:dyDescent="0.25">
+    <row r="418" spans="18:33" x14ac:dyDescent="0.3">
       <c r="R418" s="10"/>
       <c r="S418" s="10"/>
       <c r="T418" s="10"/>
@@ -42843,7 +42886,7 @@
     <mergeCell ref="AB1:AC1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B4:K408 M4:Q408">
+  <conditionalFormatting sqref="M4:Q408 B4:K408">
     <cfRule type="expression" dxfId="23" priority="41">
       <formula>$B4=2</formula>
     </cfRule>
@@ -42970,292 +43013,292 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A9A9A2-AF59-4E23-8473-E3235F07F470}">
   <dimension ref="A1:A57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
     </row>
   </sheetData>
@@ -43265,26 +43308,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="fd7a431a-ac48-40c9-8cfb-fb570019eb11" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c220fbd3-771c-45fb-b226-1e7078e429df">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DBAF84C653C70648848D5CE3F55E0766" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="c32e246f0697ea5fff0ff7310475e255">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fd7a431a-ac48-40c9-8cfb-fb570019eb11" xmlns:ns3="c220fbd3-771c-45fb-b226-1e7078e429df" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f2dffe092b16b70d30aebcfa0a94d9c9" ns2:_="" ns3:_="">
     <xsd:import namespace="fd7a431a-ac48-40c9-8cfb-fb570019eb11"/>
@@ -43519,26 +43542,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F5B731-90EB-4058-9385-4A87D458D64A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fd7a431a-ac48-40c9-8cfb-fb570019eb11"/>
-    <ds:schemaRef ds:uri="c220fbd3-771c-45fb-b226-1e7078e429df"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EB9E8F0-F327-4E84-B990-6EC8B9560054}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="fd7a431a-ac48-40c9-8cfb-fb570019eb11" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c220fbd3-771c-45fb-b226-1e7078e429df">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B10762B-3A52-4D91-AC69-FE0CB85E07A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -43555,4 +43579,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EB9E8F0-F327-4E84-B990-6EC8B9560054}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F5B731-90EB-4058-9385-4A87D458D64A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fd7a431a-ac48-40c9-8cfb-fb570019eb11"/>
+    <ds:schemaRef ds:uri="c220fbd3-771c-45fb-b226-1e7078e429df"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>